--- a/exports/OBEROIRLTY_full_report.xlsx
+++ b/exports/OBEROIRLTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.86</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>936.35</v>
+        <v>901</v>
       </c>
       <c r="I2" t="n">
         <v>907.4453671772839</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.04</v>
+        <v>-3.81</v>
       </c>
       <c r="L2" t="n">
-        <v>2.48</v>
+        <v>4.32</v>
       </c>
       <c r="M2" t="n">
         <v>0.66</v>
       </c>
       <c r="N2" t="n">
-        <v>3.91</v>
+        <v>5.16</v>
       </c>
       <c r="O2" t="n">
         <v>3.71</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>10.41</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>942.25</v>
+        <v>969</v>
       </c>
       <c r="I3" t="n">
         <v>960.0875752485503</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.58</v>
+        <v>-7.55</v>
       </c>
       <c r="L3" t="n">
-        <v>6.84</v>
+        <v>8.1</v>
       </c>
       <c r="M3" t="n">
         <v>1.56</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.49</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>895.6</v>
+        <v>862</v>
       </c>
       <c r="I4" t="n">
         <v>876.4376640760859</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.57</v>
+        <v>-11.04</v>
       </c>
       <c r="L4" t="n">
-        <v>10.21</v>
+        <v>11.15</v>
       </c>
       <c r="M4" t="n">
         <v>1.16</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.03</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>876</v>
+        <v>909.5</v>
       </c>
       <c r="I5" t="n">
         <v>885.751712337388</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.62</v>
+        <v>-5.51</v>
       </c>
       <c r="L5" t="n">
         <v>9.01</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.24</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>960.8</v>
+        <v>930.9</v>
       </c>
       <c r="I6" t="n">
         <v>936.6104437203691</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K6" t="n">
-        <v>5.64</v>
+        <v>2.35</v>
       </c>
       <c r="L6" t="n">
         <v>4.67</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.85</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>781.8</v>
+        <v>795.55</v>
       </c>
       <c r="I7" t="n">
         <v>782.4250175384039</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K7" t="n">
-        <v>16.02</v>
+        <v>14.54</v>
       </c>
       <c r="L7" t="n">
         <v>5.81</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1013.3</v>
+        <v>1008</v>
       </c>
       <c r="I8" t="n">
         <v>1012.424343523885</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>74</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>27.37</v>
+        <v>26.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.89</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44865.38541666666</v>
+        <v>44865.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>918.85</v>
+        <v>926.95</v>
       </c>
       <c r="I9" t="n">
         <v>920.5607580622658</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>8.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>4.28</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44875.38541666666</v>
+        <v>44875.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>886.15</v>
+        <v>872.1</v>
       </c>
       <c r="I10" t="n">
         <v>883.5018630200939</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.4</v>
+        <v>-5.92</v>
       </c>
       <c r="L10" t="n">
         <v>8.06</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>900.4</v>
+        <v>928.55</v>
       </c>
       <c r="I11" t="n">
         <v>917.5168532346587</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.25</v>
+        <v>-6.47</v>
       </c>
       <c r="L11" t="n">
-        <v>5.91</v>
+        <v>7.81</v>
       </c>
       <c r="M11" t="n">
         <v>1.36</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>6.7</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>908.35</v>
+        <v>901.2</v>
       </c>
       <c r="I12" t="n">
         <v>902.6902274519166</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.18</v>
+        <v>-2.95</v>
       </c>
       <c r="L12" t="n">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="M12" t="n">
         <v>0.22</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>5.89</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>801</v>
+        <v>846.4</v>
       </c>
       <c r="I13" t="n">
         <v>846.2496544539609</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>52</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>11.12</v>
+        <v>6.08</v>
       </c>
       <c r="L13" t="n">
         <v>3.08</v>
       </c>
       <c r="M13" t="n">
-        <v>1.13</v>
+        <v>2.86</v>
       </c>
       <c r="N13" t="n">
         <v>2.46</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.33</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>862.5</v>
+        <v>850</v>
       </c>
       <c r="I14" t="n">
         <v>856.4227008270018</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9</v>
+        <v>0.43</v>
       </c>
       <c r="L14" t="n">
         <v>4.62</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.25</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>842.65</v>
+        <v>863.4</v>
       </c>
       <c r="I15" t="n">
         <v>858.1941213698991</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>0.86</v>
+        <v>-1.58</v>
       </c>
       <c r="L15" t="n">
         <v>2.64</v>
@@ -1296,7 +1475,7 @@
         <v>0.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
         <v>-1.33</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.13</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>910.2</v>
+        <v>873</v>
       </c>
       <c r="I16" t="n">
         <v>879.8682915547097</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>5.42</v>
+        <v>1.11</v>
       </c>
       <c r="L16" t="n">
         <v>2.54</v>
@@ -1353,7 +1544,7 @@
         <v>0.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>4.03</v>
       </c>
       <c r="O16" t="n">
         <v>2.01</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.82</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="I17" t="n">
         <v>929.0658204368048</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.96</v>
+        <v>-6.87</v>
       </c>
       <c r="L17" t="n">
-        <v>6.83</v>
+        <v>7.79</v>
       </c>
       <c r="M17" t="n">
         <v>1.74</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.73</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>972.3</v>
+        <v>918.7</v>
       </c>
       <c r="I18" t="n">
         <v>937.1100257759877</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>4.21</v>
+        <v>-1.53</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="M18" t="n">
         <v>0.31</v>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>5.74</v>
       </c>
       <c r="O18" t="n">
         <v>-0.43</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.81</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>941.6</v>
+        <v>956</v>
       </c>
       <c r="I19" t="n">
         <v>955.0227633795371</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.49</v>
+        <v>-4.06</v>
       </c>
       <c r="L19" t="n">
         <v>5.96</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.25</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1194.85</v>
+        <v>1136.8</v>
       </c>
       <c r="I20" t="n">
         <v>1138.775605626541</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>102</v>
       </c>
       <c r="K20" t="n">
-        <v>24.98</v>
+        <v>18.91</v>
       </c>
       <c r="L20" t="n">
         <v>1.54</v>
@@ -1581,7 +1820,7 @@
         <v>2.87</v>
       </c>
       <c r="N20" t="n">
-        <v>2.67</v>
+        <v>4.93</v>
       </c>
       <c r="O20" t="n">
         <v>1.85</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45229.55208333334</v>
+        <v>45230.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1121.15</v>
+        <v>1132.9</v>
       </c>
       <c r="I21" t="n">
         <v>1130.46420300561</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K21" t="n">
-        <v>1.38</v>
+        <v>0.34</v>
       </c>
       <c r="L21" t="n">
         <v>5.31</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1409.05</v>
+        <v>1378.65</v>
       </c>
       <c r="I22" t="n">
         <v>1403.111109489787</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>24.38</v>
+        <v>21.69</v>
       </c>
       <c r="L22" t="n">
         <v>1.36</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.83</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45294.38541666666</v>
+        <v>45294.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1459</v>
+        <v>1461.95</v>
       </c>
       <c r="I23" t="n">
         <v>1460.627409594927</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.83</v>
+        <v>-6.04</v>
       </c>
       <c r="L23" t="n">
         <v>6.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1500</v>
+        <v>1367.5</v>
       </c>
       <c r="I24" t="n">
         <v>1479.522150046145</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>-6.46</v>
       </c>
       <c r="L24" t="n">
-        <v>0.71</v>
+        <v>6.94</v>
       </c>
       <c r="M24" t="n">
-        <v>0.57</v>
+        <v>3.67</v>
       </c>
       <c r="N24" t="n">
-        <v>2.49</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>0.55</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.74</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45344.38541666666</v>
+        <v>45344.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1366.45</v>
+        <v>1381.1</v>
       </c>
       <c r="I25" t="n">
         <v>1379.22988316771</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08</v>
+        <v>-0.99</v>
       </c>
       <c r="L25" t="n">
         <v>6.03</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>6.98</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1316.65</v>
+        <v>1298.65</v>
       </c>
       <c r="I26" t="n">
         <v>1308.531701053076</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.67</v>
+        <v>-5.97</v>
       </c>
       <c r="L26" t="n">
-        <v>5.98</v>
+        <v>7.02</v>
       </c>
       <c r="M26" t="n">
         <v>0.46</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.98</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45371.55208333334</v>
+        <v>45372.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1383</v>
+        <v>1400</v>
       </c>
       <c r="I27" t="n">
         <v>1389.23237022263</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.5</v>
+        <v>-7.8</v>
       </c>
       <c r="L27" t="n">
-        <v>6.95</v>
+        <v>8.48</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.26</v>
+        <v>3.04</v>
       </c>
       <c r="O27" t="n">
         <v>-2.14</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.32</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45398.55208333334</v>
+        <v>45400.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1464.6</v>
+        <v>1434</v>
       </c>
       <c r="I28" t="n">
         <v>1458.262928578874</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>4.61</v>
+        <v>2.43</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -2037,7 +2372,7 @@
         <v>1.73</v>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>4.14</v>
       </c>
       <c r="O28" t="n">
         <v>3.04</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>7.38</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1427.85</v>
+        <v>1473.75</v>
       </c>
       <c r="I29" t="n">
         <v>1472.941474609659</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.43</v>
+        <v>-2.77</v>
       </c>
       <c r="L29" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="M29" t="n">
         <v>0.39</v>
       </c>
       <c r="N29" t="n">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="O29" t="n">
         <v>-4.14</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.59</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1877.4</v>
+        <v>1729.6</v>
       </c>
       <c r="I30" t="n">
         <v>1751.047654450707</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K30" t="n">
-        <v>27.39</v>
+        <v>17.36</v>
       </c>
       <c r="L30" t="n">
         <v>3.52</v>
@@ -2151,7 +2510,7 @@
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.96</v>
+        <v>6.65</v>
       </c>
       <c r="O30" t="n">
         <v>3.05</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>12.7</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1744.9</v>
+        <v>1789.7</v>
       </c>
       <c r="I31" t="n">
         <v>1768.024884830525</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.88</v>
+        <v>-3.47</v>
       </c>
       <c r="L31" t="n">
         <v>12.92</v>
       </c>
       <c r="M31" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="N31" t="n">
         <v>5.33</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1773.3</v>
+        <v>1703.85</v>
       </c>
       <c r="I32" t="n">
         <v>1742.491978063255</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.92</v>
+        <v>-4.8</v>
       </c>
       <c r="L32" t="n">
         <v>6.57</v>
@@ -2265,7 +2648,7 @@
         <v>2.27</v>
       </c>
       <c r="N32" t="n">
-        <v>3.73</v>
+        <v>4.14</v>
       </c>
       <c r="O32" t="n">
         <v>-3.33</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45539.55208333334</v>
+        <v>45540.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1783</v>
+        <v>1788.4</v>
       </c>
       <c r="I33" t="n">
         <v>1784.733339564795</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.65</v>
+        <v>-4.96</v>
       </c>
       <c r="L33" t="n">
         <v>7.27</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.66</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1892.9</v>
+        <v>1843.2</v>
       </c>
       <c r="I34" t="n">
         <v>1845.882867924706</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K34" t="n">
-        <v>5.84</v>
+        <v>3.06</v>
       </c>
       <c r="L34" t="n">
         <v>3.88</v>
       </c>
       <c r="M34" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>2.99</v>
       </c>
       <c r="O34" t="n">
         <v>0.29</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>7.16</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1836.2</v>
+        <v>1884.6</v>
       </c>
       <c r="I35" t="n">
         <v>1852.133552012019</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>0.38</v>
+        <v>-2.25</v>
       </c>
       <c r="L35" t="n">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="M35" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="N35" t="n">
         <v>3.86</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.55</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45614.38541666666</v>
+        <v>45614.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>1942.35</v>
+        <v>1915</v>
       </c>
       <c r="I36" t="n">
         <v>1918.887123298773</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>3.06</v>
+        <v>1.61</v>
       </c>
       <c r="L36" t="n">
         <v>2.09</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45628.38541666666</v>
+        <v>45628.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>2035.3</v>
+        <v>2079</v>
       </c>
       <c r="I37" t="n">
         <v>2068.263334519767</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.28</v>
+        <v>-8.56</v>
       </c>
       <c r="L37" t="n">
-        <v>7.25</v>
+        <v>8.85</v>
       </c>
       <c r="M37" t="n">
         <v>3.86</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2240</v>
+        <v>2157.55</v>
       </c>
       <c r="I38" t="n">
         <v>2180.453185405289</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>7.74</v>
+        <v>3.78</v>
       </c>
       <c r="L38" t="n">
         <v>2.31</v>
@@ -2607,7 +3062,7 @@
         <v>1.49</v>
       </c>
       <c r="N38" t="n">
-        <v>1.88</v>
+        <v>5.04</v>
       </c>
       <c r="O38" t="n">
         <v>3.97</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45735.38541666666</v>
+        <v>45735.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1600.75</v>
+        <v>1615.95</v>
       </c>
       <c r="I39" t="n">
         <v>1606.212470486425</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>25.81</v>
+        <v>25.1</v>
       </c>
       <c r="L39" t="n">
         <v>4.38</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1633</v>
+        <v>1573.45</v>
       </c>
       <c r="I40" t="n">
         <v>1577.736761352176</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>1.06</v>
+        <v>-2.63</v>
       </c>
       <c r="L40" t="n">
-        <v>1.02</v>
+        <v>3.68</v>
       </c>
       <c r="M40" t="n">
         <v>0.29</v>
       </c>
       <c r="N40" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="O40" t="n">
         <v>3.04</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.07</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1541</v>
+        <v>1600.8</v>
       </c>
       <c r="I41" t="n">
         <v>1599.93461505303</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>2.06</v>
+        <v>-1.74</v>
       </c>
       <c r="L41" t="n">
         <v>3.91</v>
@@ -2778,7 +3269,7 @@
         <v>3.71</v>
       </c>
       <c r="N41" t="n">
-        <v>3.36</v>
+        <v>5.84</v>
       </c>
       <c r="O41" t="n">
         <v>-3.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>9.6</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45775.55208333334</v>
+        <v>45776.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1659.6</v>
+        <v>1586.9</v>
       </c>
       <c r="I42" t="n">
         <v>1588.113191155102</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>3.67</v>
+        <v>-0.87</v>
       </c>
       <c r="L42" t="n">
         <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>1.03</v>
+        <v>3.59</v>
       </c>
       <c r="N42" t="n">
         <v>4.42</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1632</v>
+        <v>1661.5</v>
       </c>
       <c r="I43" t="n">
         <v>1637.502958583544</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.84</v>
+        <v>-4.7</v>
       </c>
       <c r="L43" t="n">
         <v>5.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.43</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45839.55208333334</v>
+        <v>45840.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1919.8</v>
+        <v>1887.6</v>
       </c>
       <c r="I44" t="n">
         <v>1890.724167116514</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K44" t="n">
-        <v>15.55</v>
+        <v>13.61</v>
       </c>
       <c r="L44" t="n">
         <v>2.12</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.72</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1649</v>
+        <v>1664.2</v>
       </c>
       <c r="I45" t="n">
         <v>1658.525934466247</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K45" t="n">
-        <v>12.64</v>
+        <v>11.84</v>
       </c>
       <c r="L45" t="n">
         <v>1.76</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>4.92</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45898.38541666666</v>
+        <v>45898.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1615.4</v>
+        <v>1607</v>
       </c>
       <c r="I46" t="n">
         <v>1609.004760085093</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.93</v>
+        <v>-3.44</v>
       </c>
       <c r="L46" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="M46" t="n">
         <v>0.38</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.68</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45919.38541666666</v>
+        <v>45919.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1655.6</v>
+        <v>1672</v>
       </c>
       <c r="I47" t="n">
         <v>1665.408143989746</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.02</v>
+        <v>-4.04</v>
       </c>
       <c r="L47" t="n">
         <v>4.85</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.37</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1606.4</v>
+        <v>1600</v>
       </c>
       <c r="I48" t="n">
         <v>1604.95453023282</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.92</v>
+        <v>-4.31</v>
       </c>
       <c r="L48" t="n">
         <v>4.85</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1609.2</v>
+        <v>1678.9</v>
       </c>
       <c r="I49" t="n">
         <v>1641.948157310636</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.58</v>
+        <v>-4.93</v>
       </c>
       <c r="L49" t="n">
-        <v>2.62</v>
+        <v>5.98</v>
       </c>
       <c r="M49" t="n">
-        <v>1.05</v>
+        <v>4.09</v>
       </c>
       <c r="N49" t="n">
-        <v>2.26</v>
+        <v>5.15</v>
       </c>
       <c r="O49" t="n">
         <v>-1.23</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.96</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45978.55208333334</v>
+        <v>45979.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1752</v>
+        <v>1711</v>
       </c>
       <c r="I50" t="n">
         <v>1730.931518847081</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K50" t="n">
-        <v>4.35</v>
+        <v>1.91</v>
       </c>
       <c r="L50" t="n">
         <v>1.66</v>
@@ -3291,7 +3890,7 @@
         <v>1.35</v>
       </c>
       <c r="N50" t="n">
-        <v>1.81</v>
+        <v>2.57</v>
       </c>
       <c r="O50" t="n">
         <v>5.15</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.78</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46015.55208333334</v>
+        <v>46017.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1671.9</v>
+        <v>1686.8</v>
       </c>
       <c r="I51" t="n">
         <v>1684.919407330729</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>2.29</v>
+        <v>1.41</v>
       </c>
       <c r="L51" t="n">
         <v>2.45</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.87</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1695.8</v>
+        <v>1647.6</v>
       </c>
       <c r="I52" t="n">
         <v>1661.838040733785</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K52" t="n">
-        <v>0.53</v>
+        <v>-2.32</v>
       </c>
       <c r="L52" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="M52" t="n">
         <v>1.5</v>
       </c>
       <c r="N52" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="O52" t="n">
         <v>0.82</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.04</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46057.55208333334</v>
+        <v>46058.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1540.8</v>
+        <v>1549.6</v>
       </c>
       <c r="I53" t="n">
         <v>1549.310318907333</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>6.48</v>
+        <v>5.95</v>
       </c>
       <c r="L53" t="n">
         <v>2.62</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>7.97</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1525</v>
+        <v>1474.7</v>
       </c>
       <c r="I54" t="n">
         <v>1488.950223333577</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.59</v>
+        <v>-4.83</v>
       </c>
       <c r="L54" t="n">
-        <v>3.66</v>
+        <v>5.01</v>
       </c>
       <c r="M54" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="N54" t="n">
         <v>2.45</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.28</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46114.38541666666</v>
+        <v>46114.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1477.6</v>
+        <v>1512</v>
       </c>
       <c r="I55" t="n">
         <v>1503.881996539903</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.2</v>
+        <v>-2.53</v>
       </c>
       <c r="L55" t="n">
         <v>2.85</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.42</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1657.9</v>
+        <v>1632.1</v>
       </c>
       <c r="I56" t="n">
         <v>1636.071626718785</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K56" t="n">
-        <v>9.65</v>
+        <v>7.94</v>
       </c>
       <c r="L56" t="n">
         <v>2.45</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.17</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1659.8</v>
+        <v>1709.7</v>
       </c>
       <c r="I57" t="n">
         <v>1687.451215034013</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.7</v>
+        <v>-4.75</v>
       </c>
       <c r="L57" t="n">
         <v>4.9</v>
@@ -3690,7 +4373,7 @@
         <v>2.26</v>
       </c>
       <c r="N57" t="n">
-        <v>1.49</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>-4.56</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.84</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>1626.2</v>
+        <v>1594.4</v>
       </c>
       <c r="I58" t="n">
         <v>1621.870943307874</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.88</v>
+        <v>-6.74</v>
       </c>
       <c r="L58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M58" t="n">
         <v>1.22</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>6.58</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1632</v>
+        <v>1675.8</v>
       </c>
       <c r="I59" t="n">
         <v>1669.98312249967</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.36</v>
+        <v>-5.11</v>
       </c>
       <c r="L59" t="n">
-        <v>2.88</v>
+        <v>6.31</v>
       </c>
       <c r="M59" t="n">
-        <v>0.63</v>
+        <v>2.39</v>
       </c>
       <c r="N59" t="n">
         <v>2.8</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.16</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46224.55208333334</v>
+        <v>46225.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1884.9</v>
+        <v>1847.6</v>
       </c>
       <c r="I60" t="n">
         <v>1856.914741267269</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K60" t="n">
-        <v>12.48</v>
+        <v>10.25</v>
       </c>
       <c r="L60" t="n">
         <v>1.54</v>
@@ -3861,7 +4580,7 @@
         <v>2.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="O60" t="n">
         <v>2.54</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46247.38541666666</v>
+        <v>46247.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1828.1</v>
+        <v>1844.9</v>
       </c>
       <c r="I61" t="n">
         <v>1842.06803640413</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>1.06</v>
+        <v>0.15</v>
       </c>
       <c r="L61" t="n">
         <v>2.4</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.03</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1830</v>
+        <v>1818.8</v>
       </c>
       <c r="I62" t="n">
         <v>1822.859116818002</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="L62" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="M62" t="n">
         <v>0.59</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.54</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1759</v>
+        <v>1806.8</v>
       </c>
       <c r="I63" t="n">
         <v>1779.678603900518</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>3.29</v>
+        <v>0.66</v>
       </c>
       <c r="L63" t="n">
         <v>0.96</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="N63" t="n">
-        <v>1.91</v>
+        <v>3.52</v>
       </c>
       <c r="O63" t="n">
         <v>-1.64</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.98</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1779.6</v>
+        <v>1744.1</v>
       </c>
       <c r="I64" t="n">
         <v>1756.659152251051</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.51</v>
+        <v>-3.47</v>
       </c>
       <c r="L64" t="n">
-        <v>3.06</v>
+        <v>4.25</v>
       </c>
       <c r="M64" t="n">
         <v>1.09</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>36</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.3</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.4</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7098,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7118,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65.09999999999999</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.13</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.29</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.39</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.6</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.03</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="21">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.22</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.14</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
